--- a/OUTWASH/Risultati Ottimizzazione.xlsx
+++ b/OUTWASH/Risultati Ottimizzazione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silvi\OneDrive\Documenti\GitHub\progettoAerodinamico\OUTWASH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e3273853c0319ce0/Documenti/GitHub/progettoAerodinamico/OUTWASH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2778773D-7AA0-47D2-AD63-A00B0E9FDA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2778773D-7AA0-47D2-AD63-A00B0E9FDA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9449286-B013-493F-BDB1-45D8EC8BCE20}"/>
   <bookViews>
-    <workbookView xWindow="1572" yWindow="696" windowWidth="16764" windowHeight="8880" xr2:uid="{942A9D3C-7315-4E4F-9189-62CC279747F8}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{942A9D3C-7315-4E4F-9189-62CC279747F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,16 +586,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77815054-0117-4375-B038-D934A66EAA82}">
   <dimension ref="B1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="3" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.9140625" style="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:6" ht="15" thickBot="1"/>
+    <row r="2" spans="2:6" ht="15.65">
       <c r="B2" s="10" t="s">
         <v>12</v>
       </c>
@@ -604,7 +605,7 @@
       <c r="E2" s="11"/>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="15.65">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -621,7 +622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="14.4">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -638,7 +639,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14.4">
       <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
@@ -655,7 +656,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14.4">
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
@@ -672,7 +673,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14.4">
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
@@ -689,7 +690,7 @@
         <v>0.41799999999999998</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14.4">
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
@@ -706,7 +707,7 @@
         <v>0.46600000000000003</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="14.4">
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
@@ -723,7 +724,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14.4">
       <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
@@ -740,7 +741,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14.4">
       <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
@@ -757,7 +758,7 @@
         <v>0.48499999999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14.4">
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -774,7 +775,7 @@
         <v>0.38200000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="14.4">
       <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
@@ -791,7 +792,7 @@
         <v>0.46500000000000002</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" ht="15" thickBot="1">
       <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
@@ -808,8 +809,8 @@
         <v>0.63800000000000001</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="15" thickBot="1"/>
+    <row r="16" spans="2:6" ht="15.65">
       <c r="B16" s="10" t="s">
         <v>17</v>
       </c>
@@ -818,7 +819,7 @@
       <c r="E16" s="11"/>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="15.65">
       <c r="B17" s="2" t="s">
         <v>0</v>
       </c>
@@ -835,67 +836,67 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14.4">
       <c r="B18" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14.4">
       <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="14.4">
       <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="14.4">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="14.4">
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="14.4">
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6">
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6">
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="B27" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" ht="14.5" thickBot="1">
       <c r="B28" s="7" t="s">
         <v>16</v>
       </c>
